--- a/www/download/COUNTRY.SVN.zdW13.xlsx
+++ b/www/download/COUNTRY.SVN.zdW13.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>Eslovênia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.49387592371311</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.564464649528101</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.659121935129566</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.692520748907331</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.756629938465452</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.92447928619047</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.01182824043428</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.00081058753711</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.863125422093881</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.802021157505804</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.802903282049704</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.796438372834759</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.729659977856526</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.679902081177344</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.716948718120329</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.918</t>
+          <t>-0.082127456077376</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>-0.0466404675041922</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.883</t>
+          <t>0.0815766088716274</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.881</t>
+          <t>0.0285376986011805</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.893</t>
+          <t>0.0538781114807676</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.905</t>
+          <t>0.0288216882805246</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.909</t>
+          <t>-0.0403409420939785</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.923</t>
+          <t>-0.0201546501955667</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.919</t>
+          <t>-0.0869073067598637</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.922</t>
+          <t>-0.0210322652159942</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.03383983124266</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.934</t>
+          <t>0.090664711463929</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.962</t>
+          <t>0.13098922966922</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.994</t>
+          <t>-0.182293006483285</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.974</t>
+          <t>-0.172641533998085</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.742</t>
+          <t>0.869134621523698</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.731</t>
+          <t>0.927785972400904</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>1.17230223063686</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.714</t>
+          <t>1.06256418145084</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.724</t>
+          <t>1.06816075607121</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.738</t>
+          <t>1.12493392836179</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.746</t>
+          <t>1.00481921801889</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.756</t>
+          <t>1.01805830763422</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.756</t>
+          <t>0.84611556480919</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.759</t>
+          <t>0.967450964332257</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>1.07171140233158</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>1.06987905487219</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.797</t>
+          <t>1.13345719930627</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.821</t>
+          <t>0.522803084435268</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.801</t>
+          <t>0.560415463134497</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1708.758</t>
+          <t>1.64951361331779</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1670.15</t>
+          <t>1.72914601578082</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1638.628</t>
+          <t>2.12489029417878</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1629.509</t>
+          <t>1.95500155750618</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1644.428</t>
+          <t>2.08928857441758</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1660.151</t>
+          <t>2.03490072330501</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1662.069</t>
+          <t>1.86479295362879</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1682.333</t>
+          <t>1.82218389335035</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1671.121</t>
+          <t>1.58471286563271</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1671.611</t>
+          <t>1.77156063970986</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1664.697</t>
+          <t>1.89648173715877</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1689.328</t>
+          <t>1.90640841604813</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>1740.358</t>
+          <t>1.77855776124857</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1819.538</t>
+          <t>1.03880709958542</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1778.476</t>
+          <t>1.14587906098868</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1287.888</t>
+          <t>2271737317.55048</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1269.261</t>
+          <t>2212462277.53077</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1237.461</t>
+          <t>2068500113.47739</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1237.419</t>
+          <t>2081133071.28026</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1255.282</t>
+          <t>2084073698.62559</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1280.997</t>
+          <t>2178751872.81576</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1294.77</t>
+          <t>2185970776.91513</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1311.437</t>
+          <t>2161116828.80111</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1313.919</t>
+          <t>2271907977.16954</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1319.254</t>
+          <t>2250576644.27981</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1322.093</t>
+          <t>2222370142.61307</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1343.542</t>
+          <t>2301628466.09459</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1387.787</t>
+          <t>2402259919.54358</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1430.053</t>
+          <t>2590360643.68915</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1393.705</t>
+          <t>2239901337.43184</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>778111309.925446</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>744795382.147985</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>643883822.467034</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>679045891.402273</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>688263280.433403</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>27.94</t>
+          <t>704050531.203129</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>23.06</t>
+          <t>735908036.686006</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>25.74</t>
+          <t>748953778.0551</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>28.58</t>
+          <t>838849930.33722</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>796684703.672169</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>765782199.185973</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>772292635.986929</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>31.42</t>
+          <t>777763535.253551</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>32.17</t>
+          <t>1115923153.59134</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>34.16</t>
+          <t>1075698696.91584</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>62.44</t>
+          <t>1901247.93521574</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>62.44</t>
+          <t>1853240.19948715</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>62.44</t>
+          <t>1795454.92276481</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>62.44</t>
+          <t>1764502.67971186</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>62.86</t>
+          <t>1842464.44044857</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>60.34</t>
+          <t>1988392.8807056</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>63.84</t>
+          <t>1983798.27437884</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>62.09</t>
+          <t>1808618.80232487</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>60.03</t>
+          <t>1600783.87205098</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>59.41</t>
+          <t>1361917.88336503</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>59.05</t>
+          <t>1250512.59000006</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>59.21</t>
+          <t>1183265.22931054</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>58.44</t>
+          <t>983378.26112974</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>955724.471511372</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>1010093.74663068</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>10100.0194031466</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>9754.33533018511</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>9517.13813510647</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>12.87</t>
+          <t>9282.16609556519</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>11.43</t>
+          <t>9616.72238000603</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>11.72</t>
+          <t>9756.2141047764</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>9425.65515715225</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>12.17</t>
+          <t>9503.49364346187</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>10030.9064292164</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>10.54</t>
+          <t>10936.0496957881</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>11664.8198915551</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>12186.6749583869</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>13996.0628087658</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>16095.1963610001</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>14204.4207088353</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>14.68</t>
+          <t>19574.3532241692</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>14.68</t>
+          <t>19200.0646337458</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>14.68</t>
+          <t>17893.1499958675</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>14.68</t>
+          <t>17820.8252575326</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>15.34</t>
+          <t>18562.795397257</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>19726.9977181084</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>13.47</t>
+          <t>19221.944510169</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>14.89</t>
+          <t>19418.2187729392</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>21884.217103768</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>17.99</t>
+          <t>23844.7371631567</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>18.69</t>
+          <t>25219.028245417</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>27266.6690638328</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>32065.6778871168</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>20.94</t>
+          <t>37854.8647111493</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>22.37</t>
+          <t>30514.082361802</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>66.96</t>
+          <t>0.655145789572406</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>66.96</t>
+          <t>0.704173436422127</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>66.96</t>
+          <t>0.921869795486186</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>66.96</t>
+          <t>0.822291307927175</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>67.97</t>
+          <t>0.823839794934956</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>66.73</t>
+          <t>0.819467105290676</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>67.95</t>
+          <t>0.759417965375601</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>0.751024954771597</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>66.69</t>
+          <t>0.566334367095443</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>66.61</t>
+          <t>0.655929392159982</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>66.58</t>
+          <t>0.72646051225672</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>66.35</t>
+          <t>0.739679520682853</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>65.87</t>
+          <t>0.784330522524147</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>65.14</t>
+          <t>0.281498139750258</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>0.295627660911696</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>16.69</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>16.96</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>18.59</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>17.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>16.36</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>14.73</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>13.92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>13.23</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.49387592371311</t>
+          <t>1049.3024888719</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.564464649528101</t>
+          <t>1018.93744488084</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.659121935129566</t>
+          <t>902.344026731907</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.692520748907331</t>
+          <t>951.629771529375</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.756629938465452</t>
+          <t>951.271881503323</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.92447928619047</t>
+          <t>953.424404833852</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.01182824043428</t>
+          <t>986.61737881726</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.00081058753711</t>
+          <t>991.194864599057</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.863125422093881</t>
+          <t>1109.11598660522</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.802021157505804</t>
+          <t>1049.25924019393</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.802903282049704</t>
+          <t>1007.14434035112</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796438372834759</t>
+          <t>999.95032698018</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729659977856526</t>
+          <t>975.72924094987</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679902081177344</t>
+          <t>1359.72281383471</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.716948718120329</t>
+          <t>1343.73986218541</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>200382816.906996</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>228048477.013492</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>138847698.414513</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>207677602.358926</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>202693135.787819</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>231787981.446792</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>294212600.258314</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>408198093.715231</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>533270265.43721</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>401985384.380354</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>386937497.757362</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>434155745.222254</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>491114657.134955</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>806224206.356219</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>813475913.661219</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>236763296.973469</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>259150235.577763</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>168362605.170067</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>245394139.51722</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>240874752.761545</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>264677581.733409</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>337632944.909729</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>453234093.161556</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>594933543.464001</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>440553921.191751</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>437550126.567046</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>477020329.985141</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>535425789.436376</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>822725675.328501</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>837639760.435264</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>-36380480.0664724</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>-31101758.5642713</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>-29514906.7555544</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>-37716537.158294</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>-38181616.9737258</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>-32889600.2866173</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>-43420344.6514154</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>-45035999.4463256</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>-61663278.0267914</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>-38568536.8113972</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>-50612628.8096835</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>-42864584.7628876</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>-44311132.3014211</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>-16501468.9722818</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>-24163846.774045</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>1736.74859644417</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>1736.44612694176</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>1734.18773011343</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>1734.1466610227</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>1734.96751328841</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>1734.72434197653</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>1735.87234124287</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>1735.6069429544</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>1737.24648691473</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>1737.49921583258</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>1738.79493375905</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>1739.59310554754</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>1741.02346634617</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>1742.48225650517</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>1740.98653451709</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>1861.19103256454</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>1856.72498734705</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>1856.59990364705</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>1849.60885289455</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>1841.17032444353</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>1835.01920590413</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>1828.64145472588</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1823.0152833062</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>1817.95097208925</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>1812.84997022208</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>1808.83775663903</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>1808.39267586158</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>1808.61328754398</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>1830.09325092051</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>1826.277548343</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-8.21</t>
+          <t>9272.3561394543</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>9285.34225976318</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>8.16</t>
+          <t>9365.768802039</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>10013.910562401</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>9573.69797367611</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>9813.22345086639</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-4.03</t>
+          <t>10317.846404815</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>11657.1211508588</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-8.69</t>
+          <t>14287.0125469065</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>18044.2917899178</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>20166.8374977181</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>23576.8940889948</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>29219.0397060095</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-18.23</t>
+          <t>32166.3406084947</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-17.26</t>
+          <t>24932.8159572924</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>86.91</t>
+          <t>667094771.285109</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>92.78</t>
+          <t>631807608.009982</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>117.23</t>
+          <t>613636328.90801</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>106.26</t>
+          <t>635194292.279965</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>106.82</t>
+          <t>635770897.478141</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>112.49</t>
+          <t>694098828.604551</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>100.48</t>
+          <t>725298778.2969</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>101.81</t>
+          <t>732896192.111722</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>84.61</t>
+          <t>771388830.571621</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>96.75</t>
+          <t>814039088.407884</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>107.17</t>
+          <t>843160837.890287</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>106.99</t>
+          <t>910491806.901449</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>113.35</t>
+          <t>955530904.888422</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>52.28</t>
+          <t>1033322165.13157</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>56.04</t>
+          <t>837355172.55187</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>164.95</t>
+          <t>9797.41148269065</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>172.91</t>
+          <t>9722.74805747548</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>212.49</t>
+          <t>9752.39271097419</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>195.5</t>
+          <t>10389.181562587</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>208.93</t>
+          <t>10471.0286433887</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>203.49</t>
+          <t>10541.5333387254</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>186.48</t>
+          <t>10558.6099646328</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>182.22</t>
+          <t>11480.3334118506</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>158.47</t>
+          <t>14456.1382515723</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>177.16</t>
+          <t>18654.9436607727</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>189.65</t>
+          <t>20708.9772832165</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>190.64</t>
+          <t>24089.404044779</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>177.86</t>
+          <t>30342.3600938279</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>103.88</t>
+          <t>34397.0564148913</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>114.59</t>
+          <t>24863.4479545927</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1708.758</t>
+          <t>939840309.182932</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1670.15</t>
+          <t>917676071.631273</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1638.628</t>
+          <t>799268556.902847</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1629.509</t>
+          <t>891039562.64759</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1644.428</t>
+          <t>956349439.119557</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1660.151</t>
+          <t>1022765724.37597</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1662.069</t>
+          <t>1053254242.61927</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1682.333</t>
+          <t>1116592458.94433</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1671.121</t>
+          <t>1326928569.56347</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1671.611</t>
+          <t>1289972285.50184</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1664.697</t>
+          <t>1290900369.53119</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1689.328</t>
+          <t>1397219602.15917</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>1740.358</t>
+          <t>1548628354.44785</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>1819.538</t>
+          <t>2021869950.46798</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1778.476</t>
+          <t>1644587152.07361</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1287.888</t>
+          <t>-525.055343236346</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1269.261</t>
+          <t>-437.405797712301</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1237.461</t>
+          <t>-386.623908935183</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1237.419</t>
+          <t>-375.271000185987</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1255.282</t>
+          <t>-897.330669712611</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1280.997</t>
+          <t>-728.309887858981</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1294.77</t>
+          <t>-240.763559817807</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1311.437</t>
+          <t>176.787739008212</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1313.919</t>
+          <t>-169.125704665741</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1319.254</t>
+          <t>-610.651870854832</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1322.093</t>
+          <t>-542.139785498375</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1343.542</t>
+          <t>-512.509955784204</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>1387.787</t>
+          <t>-1123.32038781845</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>1430.053</t>
+          <t>-2230.71580639669</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1393.705</t>
+          <t>69.3680026997011</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2271.737</t>
+          <t>-272745537.897822</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2212.462</t>
+          <t>-285868463.62129</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2068.5</t>
+          <t>-185632227.994837</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2081.133</t>
+          <t>-255845270.367625</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2084.074</t>
+          <t>-320578541.641416</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2178.752</t>
+          <t>-328666895.771421</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2185.971</t>
+          <t>-327955464.322367</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2161.117</t>
+          <t>-383696266.832606</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2271.908</t>
+          <t>-555539738.991854</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2250.577</t>
+          <t>-475933197.093957</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2222.37</t>
+          <t>-447739531.640904</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2301.628</t>
+          <t>-486727795.257721</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2402.26</t>
+          <t>-593097449.559432</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2590.361</t>
+          <t>-988547785.336413</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2239.901</t>
+          <t>-807231979.52174</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>9468.17638</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>9553.40543</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>9503.65261</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>10003.98798</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>10064.26296</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>9203.21878</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>9365.37753</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>10408.59163</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>13025.09187</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>15081.76118</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>15889.79686</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>17210.51997</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>20880.94144</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>23843.3406</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>20616.80425</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1172.176</t>
+          <t>0.0674563406386974</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1124.012</t>
+          <t>0.0818803929985599</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1100.209</t>
+          <t>0.0989613572176686</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1083.98</t>
+          <t>0.101497732808614</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1079.684</t>
+          <t>0.106505753353757</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1077.527</t>
+          <t>0.105853116686051</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1071.911</t>
+          <t>0.107201433059414</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1057.675</t>
+          <t>0.111020659085467</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1041.358</t>
+          <t>0.114652445151235</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1032.195</t>
+          <t>0.110130700370746</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1027.936</t>
+          <t>0.110226235451704</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1028.699</t>
+          <t>0.114078598278381</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1048.541</t>
+          <t>0.118514430171552</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1101.374</t>
+          <t>0.10342101287403</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1042.683</t>
+          <t>0.1102837171696</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>11620.1369238212</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>11384.3056424847</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10709.4891936987</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>11083.3810905755</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>11180.7760355203</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10295.4488956846</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>10625.4286805587</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>11845.1108065973</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>14830.0951715441</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>17269.3779092422</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>18247.4300526506</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>19678.4004124698</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>23588.5602801829</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>27890.5342784981</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>26281.4710697563</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>778.111</t>
+          <t>14964.620379661</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>744.795</t>
+          <t>14513.5561779957</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>643.884</t>
+          <t>13648.5087300115</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>679.046</t>
+          <t>14067.2700511963</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>688.263</t>
+          <t>14138.4792389739</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>704.051</t>
+          <t>12828.319893295</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>735.908</t>
+          <t>13125.6410110016</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>748.954</t>
+          <t>14692.7626133391</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>838.85</t>
+          <t>18237.6396378539</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>796.685</t>
+          <t>21236.2686187478</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>765.782</t>
+          <t>22383.7224061932</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>772.293</t>
+          <t>24088.5110512577</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>777.764</t>
+          <t>28899.233180043</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>1115.923</t>
+          <t>34279.4176577063</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>1075.699</t>
+          <t>32150.0842224023</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>65.51</t>
+          <t>42389.9215887585</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>70.42</t>
+          <t>42892.9633015573</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>92.19</t>
+          <t>41831.5572499992</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>82.23</t>
+          <t>45361.851554707</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>82.38</t>
+          <t>46489.8323809797</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>81.95</t>
+          <t>43248.2268829437</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>75.94</t>
+          <t>44081.1831907078</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>48971.3232784494</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>56.63</t>
+          <t>62434.2065509712</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>65.59</t>
+          <t>75315.7892697419</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>72.65</t>
+          <t>81725.3394066407</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>73.97</t>
+          <t>88550.1288689718</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>78.43</t>
+          <t>107022.898406523</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>134173.403031698</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>29.56</t>
+          <t>98881.1982173894</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.901</t>
+          <t>14964.620379661</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.853</t>
+          <t>15003.2649727884</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.795</t>
+          <t>14922.9701872133</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.765</t>
+          <t>15173.4962760684</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.842</t>
+          <t>15701.9804444718</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.988</t>
+          <t>16350.3662923365</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.984</t>
+          <t>16979.3258268696</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.809</t>
+          <t>17620.7621463449</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1.601</t>
+          <t>17819.490583779</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>18610.3620447041</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1.251</t>
+          <t>19259.8288859295</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.183</t>
+          <t>20137.8783819463</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.983</t>
+          <t>21070.3153595469</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.956</t>
+          <t>22344.5842434324</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>21485.7949799498</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>11620.1369238212</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>11656.7466722342</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>11612.5759383847</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>11892.5620345832</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>12250.8383044423</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>12994.5453810855</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>13546.5762940706</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>14024.1579924517</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>14282.7705288857</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>14978.350651655</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>15666.1699242002</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>16387.9639260992</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>17339.2450984101</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>18317.4158893551</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>17673.1445639795</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2859.46899033896</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>3512.09269200432</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>4139.70767998852</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>4604.12508880365</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>4951.43462102615</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>4577.95960670504</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>4725.56600899841</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>5436.8285866609</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>7158.23444214607</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>8294.58062125223</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>9008.27650380679</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>10101.6745787423</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>12683.757819957</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>13876.3492422936</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>10904.9860975977</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1287887658.44177</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1269260505.82646</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1237460870.20158</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1237419425.58602</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1255281960.24692</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>1280996781.98652</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1294769820.60965</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1311436755.34495</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>1313919474.72281</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>1319253617.09501</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>1322092727.88369</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>1343541682.80064</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>1387787215.2592</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>1430053445.43154</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1393704986.53083</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1708757625.80647</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1670150120.2685</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1638627648.55927</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1629509098.6178</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1644428387.08447</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>1660151050.6775</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1662068675.97344</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1682333193.89346</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>1671120525.92652</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>1671610829.04208</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>1664696902.32574</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>1689328102.08285</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>1740358030.68536</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>1819537674.08294</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1778476269.73853</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1172176200.32428</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1124011787.04834</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1100208812.70175</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1083980262.16165</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1079684269.00381</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>1077526852.08965</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1071910634.01072</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1057674768.49686</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1041357624.38832</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1032194981.12369</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>1027936016.9503</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1028699102.39496</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>1048541086.05704</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>1101373985.19625</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1042682541.32371</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>918099</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>899514</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>882596</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>881002</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>893143</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>904705</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>908909</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>922830</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>919233</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>922090</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>920313</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>934160</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>962261</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>994232.219132951</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>973825.841177403</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>741551</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>730953</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>713568</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>713561</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>723519</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>738444</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>745890</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>755607</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>756323</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>759283</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>760350</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>772331</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>797110</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>820699</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>800526</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1708757625.80647</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1670150120.2685</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1638627648.55927</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1629509098.6178</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1644428387.08447</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>1660151050.6775</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1662068675.97344</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1682333193.89346</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>1671120525.92652</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>1671610829.04208</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>1664696902.32574</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>1689328102.08285</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>1740358030.68536</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>1819537674.08294</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1778476269.73853</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1287887658.44177</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1269260505.82646</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1237460870.20158</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1237419425.58602</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1255281960.24692</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>1280996781.98652</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1294769820.60965</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>1311436755.34495</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>1313919474.72281</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>1319253617.09501</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>1322092727.88369</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>1343541682.80064</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>1387787215.2592</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>1430053445.43154</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1393704986.53083</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.246865638342609</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.246865638342609</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.246865638342609</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.246865638342609</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.257023267552655</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.279413119243087</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.230621348589472</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.257362321072398</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.285823508591103</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.300466154223845</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.30899248679988</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.31293809402232</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.314209084368503</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.321657071696235</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.341631791924359</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.624435919070539</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.624435919070539</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.624435919070539</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.624435919070539</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.628636805898128</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.603415954512167</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.63837916359736</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.620910986397626</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.600341285626231</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.594092410633173</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.590468665356388</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.592062285047216</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.58441641414411</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.58000538446106</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.566979901880087</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.128698442586853</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.128698442586853</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.128698442586853</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.128698442586853</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.114339926549217</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.117170926244746</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.130999487813169</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.121726692529977</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.113835205782666</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.105441435142982</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.100538847843732</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.0949996209304649</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.101374501487387</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.0983375438427051</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.0913883061955541</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.146828127940186</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.146828127940186</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.146828127940186</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.146828127940186</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.153428418671205</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.163047805157799</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.134658971574206</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.148873839431078</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.169459064090797</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.179940913358341</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.186909815187493</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.198040398164625</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.202323456638045</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.209431689172736</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.223685859238385</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.669597536849742</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.669597536849742</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.669597536849742</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.669597536849742</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.679689624684062</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.66734478186268</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.679472906294703</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.678961289278051</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.666898397724071</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.666051242258056</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.665832069252872</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.663491474463731</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.658672057320843</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.651355114958407</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.643975098581195</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.183574335210072</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.183574335210072</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.183574335210072</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.183574335210072</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.166881956644733</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.16960741297952</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.185868122131091</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.172164871290872</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.163642538185132</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.154007844383604</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.147258115559636</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.138468127371644</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.139004486041112</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.139213195868857</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.132339042180419</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>40260.23086</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>40779.67183</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>39685.83759</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>41536.33577</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>41819.65685</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>39411.53714</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>40018.74467</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>44922.06561</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>56083.43718</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>65875.94685</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>70482.11437</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>78329.00244</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>97551.78466</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>112680.84917</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>95937.80408</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>17824.08937</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>18025.64887</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>17788.21641</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>18671.39514</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>19089.91386</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>17406.2795</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>17851.20702</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>20129.5912</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>25395.87408</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>29530.84924</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>31391.99891</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>34190.18563</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>41582.991</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>48155.7669</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>43055.07032</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>20935.3616311307</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>22242.2910994064</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>23780.3187472429</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>25466.5858163651</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>27496.1382046508</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>29446.0190245068</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>31307.6121063329</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>33038.5226663467</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>34925.1672613311</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>36925.5782712133</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>38932.9585921994</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>41245.4571810376</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>44221.4509312072</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>49870.5902665899</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>38591.9125511486</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW13</t>
